--- a/output/pdf_financials_xlsx/NDM.xlsx
+++ b/output/pdf_financials_xlsx/NDM.xlsx
@@ -1309,49 +1309,49 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>1.15</v>
+        <v>-1.15</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>12.715</v>
+        <v>-12.765</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>14.145</v>
+        <v>-14.085</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>20.139</v>
+        <v>-20.139</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>15.662</v>
+        <v>-15.662</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>2.523</v>
+        <v>-2.523</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>31.347</v>
+        <v>-31.347</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>33.829</v>
+        <v>-33.829</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>26.982</v>
+        <v>-26.982</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>64.86499999999999</v>
+        <v>-64.86499999999999</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>15.957</v>
+        <v>-15.957</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>69.193</v>
+        <v>-69.193</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>31.542</v>
+        <v>-31.542</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>24.549</v>
+        <v>-24.335</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>20.996</v>
+        <v>-20.996</v>
       </c>
       <c r="Q16" s="1" t="inlineStr">
         <is>
@@ -1617,49 +1617,49 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1.15</v>
+        <v>-1.15</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>12.74</v>
+        <v>-12.74</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>14.115</v>
+        <v>-14.115</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>20.139</v>
+        <v>-20.139</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>15.662</v>
+        <v>-15.662</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>2.523</v>
+        <v>-2.523</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>31.347</v>
+        <v>-31.347</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>33.829</v>
+        <v>-33.829</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>26.982</v>
+        <v>-26.982</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>64.86499999999999</v>
+        <v>-64.86499999999999</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>15.957</v>
+        <v>-15.957</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>69.193</v>
+        <v>-69.193</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>31.542</v>
+        <v>-31.542</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>24.442</v>
+        <v>-24.442</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>20.996</v>
+        <v>-20.996</v>
       </c>
       <c r="Q20" s="1" t="inlineStr">
         <is>
@@ -1803,49 +1803,49 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>1.15</v>
+        <v>-1.15</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>12.74</v>
+        <v>-12.74</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>14.115</v>
+        <v>-14.115</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>20.139</v>
+        <v>-20.139</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>15.662</v>
+        <v>-15.662</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>2.523</v>
+        <v>-2.523</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>31.347</v>
+        <v>-31.347</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>33.829</v>
+        <v>-33.829</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>26.982</v>
+        <v>-26.982</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>64.86499999999999</v>
+        <v>-64.86499999999999</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>15.957</v>
+        <v>-15.957</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>69.193</v>
+        <v>-69.193</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>31.542</v>
+        <v>-31.542</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>24.442</v>
+        <v>-24.442</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>20.996</v>
+        <v>-20.996</v>
       </c>
       <c r="Q23" s="1" t="inlineStr">
         <is>
@@ -1994,46 +1994,46 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>91</v>
+        <v>-91</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>94.09999999999999</v>
+        <v>-94.09999999999999</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>95.90000000000001</v>
+        <v>-95.90000000000001</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>97.8875</v>
+        <v>-97.8875</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>84.09999999999999</v>
+        <v>-84.09999999999999</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>94.990909</v>
+        <v>-94.990909</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>147.082609</v>
+        <v>-147.082609</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>245.290909</v>
+        <v>-245.290909</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>294.840909</v>
+        <v>-294.840909</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>319.14</v>
+        <v>-319.14</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>364.173684</v>
+        <v>-364.173684</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>525.7</v>
+        <v>-525.7</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>488.84</v>
+        <v>-488.84</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>524.9</v>
+        <v>-524.9</v>
       </c>
       <c r="Q26" s="1" t="inlineStr">
         <is>
@@ -2053,49 +2053,49 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>1.15</v>
+        <v>-1.15</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>12.715</v>
+        <v>-12.765</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>14.145</v>
+        <v>-14.085</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>20.139</v>
+        <v>-20.139</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>15.662</v>
+        <v>-15.662</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>2.523</v>
+        <v>-2.523</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>31.347</v>
+        <v>-31.347</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>33.829</v>
+        <v>-33.829</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>26.982</v>
+        <v>-26.982</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>64.86499999999999</v>
+        <v>-64.86499999999999</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>15.957</v>
+        <v>-15.957</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>69.193</v>
+        <v>-69.193</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>31.542</v>
+        <v>-31.542</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>24.549</v>
+        <v>-24.335</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>20.996</v>
+        <v>-20.996</v>
       </c>
       <c r="Q27" s="1" t="inlineStr">
         <is>
@@ -2177,49 +2177,49 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>1.154</v>
+        <v>-1.146</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>12.715</v>
+        <v>-12.765</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>14.145</v>
+        <v>-14.085</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>20.139</v>
+        <v>-20.139</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>15.662</v>
+        <v>-15.662</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>2.523</v>
+        <v>-2.523</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>31.629</v>
+        <v>-31.065</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>34.108</v>
+        <v>-33.55</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>27.187</v>
+        <v>-26.777</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>65.041</v>
+        <v>-64.68899999999999</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>16.191</v>
+        <v>-15.723</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>69.84</v>
+        <v>-68.54600000000001</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>31.871</v>
+        <v>-31.213</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>24.808</v>
+        <v>-24.076</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>21.16</v>
+        <v>-20.832</v>
       </c>
       <c r="Q29" s="1" t="inlineStr">
         <is>
@@ -2331,49 +2331,49 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0.1966181675186787</v>
+        <v>-0.1958480219349785</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0.2120890774125133</v>
+        <v>-0.2129925452609159</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0.4358629679416677</v>
+        <v>-0.4396959112389563</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q31" s="1" t="inlineStr">
         <is>
@@ -6148,49 +6148,49 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>17.378</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>36.919</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>35.114</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>48.132</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>51.129</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>58.649</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>84.03100000000001</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>99.035</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>102.821</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>95.16800000000001</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>117.796</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>107.163</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>106.735</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>118.369</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>117.292</v>
       </c>
       <c r="Q92" s="1" t="inlineStr">
         <is>
@@ -11032,7 +11032,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -12439,7 +12443,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -19106,7 +19114,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -21118,7 +21130,11 @@
           <t>Reserves 36,919</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E125" s="5" t="n">
         <v>17.378</v>
       </c>
@@ -49588,16 +49604,16 @@
         </is>
       </c>
       <c r="L412" s="5" t="n">
-        <v>33.829</v>
+        <v>-33.829</v>
       </c>
       <c r="M412" s="5" t="n">
-        <v>26.982</v>
+        <v>-26.982</v>
       </c>
       <c r="N412" s="5" t="n">
-        <v>64.86499999999999</v>
+        <v>-64.86499999999999</v>
       </c>
       <c r="O412" s="5" t="n">
-        <v>15.957</v>
+        <v>-15.957</v>
       </c>
       <c r="P412" t="inlineStr">
         <is>
@@ -49605,13 +49621,13 @@
         </is>
       </c>
       <c r="Q412" s="5" t="n">
-        <v>31.542</v>
+        <v>-31.542</v>
       </c>
       <c r="R412" s="5" t="n">
-        <v>24.442</v>
+        <v>-24.442</v>
       </c>
       <c r="S412" s="5" t="n">
-        <v>20.996</v>
+        <v>-20.996</v>
       </c>
       <c r="T412" t="inlineStr">
         <is>
@@ -52036,10 +52052,10 @@
         </is>
       </c>
       <c r="O437" s="5" t="n">
-        <v>15.957</v>
+        <v>-15.957</v>
       </c>
       <c r="P437" s="5" t="n">
-        <v>69.193</v>
+        <v>-69.193</v>
       </c>
       <c r="Q437" t="inlineStr">
         <is>
@@ -55570,28 +55586,28 @@
         </is>
       </c>
       <c r="E473" s="5" t="n">
-        <v>1.15</v>
+        <v>-1.15</v>
       </c>
       <c r="F473" s="5" t="n">
-        <v>12.74</v>
+        <v>-12.74</v>
       </c>
       <c r="G473" s="5" t="n">
-        <v>14.115</v>
+        <v>-14.115</v>
       </c>
       <c r="H473" s="5" t="n">
-        <v>20.139</v>
+        <v>-20.139</v>
       </c>
       <c r="I473" s="5" t="n">
-        <v>15.662</v>
+        <v>-15.662</v>
       </c>
       <c r="J473" s="5" t="n">
-        <v>2.523</v>
+        <v>-2.523</v>
       </c>
       <c r="K473" s="5" t="n">
-        <v>31.347</v>
+        <v>-31.347</v>
       </c>
       <c r="L473" s="5" t="n">
-        <v>33.829</v>
+        <v>-33.829</v>
       </c>
       <c r="M473" t="inlineStr">
         <is>
@@ -58056,10 +58072,10 @@
         </is>
       </c>
       <c r="H498" s="5" t="n">
-        <v>17.986</v>
+        <v>-17.986</v>
       </c>
       <c r="I498" s="5" t="n">
-        <v>17.785</v>
+        <v>-17.785</v>
       </c>
       <c r="J498" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/NDM.xlsx
+++ b/output/pdf_financials_xlsx/NDM.xlsx
@@ -1061,49 +1061,49 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-1.115</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.335</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.544</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.944</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.887</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-1.136</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.281</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.099</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.033</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.462</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.237</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.176</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.279</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.27</v>
       </c>
       <c r="Q12" s="1" t="inlineStr">
         <is>
@@ -2053,49 +2053,49 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.15</v>
+        <v>-0.035</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-12.765</v>
+        <v>-12.43</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-14.085</v>
+        <v>-13.541</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-20.139</v>
+        <v>-19.195</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-15.662</v>
+        <v>-14.775</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.523</v>
+        <v>-1.387</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-31.347</v>
+        <v>-31.066</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-33.829</v>
+        <v>-33.73</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-26.982</v>
+        <v>-26.949</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-64.86499999999999</v>
+        <v>-64.40300000000001</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-15.957</v>
+        <v>-15.273</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-69.193</v>
+        <v>-68.956</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-31.542</v>
+        <v>-31.366</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-24.335</v>
+        <v>-24.056</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-20.996</v>
+        <v>-20.726</v>
       </c>
       <c r="Q27" s="1" t="inlineStr">
         <is>
@@ -2177,49 +2177,49 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.146</v>
+        <v>-0.031</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-12.765</v>
+        <v>-12.43</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-14.085</v>
+        <v>-13.541</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-20.139</v>
+        <v>-19.195</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-15.662</v>
+        <v>-14.775</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.523</v>
+        <v>-1.387</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-31.065</v>
+        <v>-30.784</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-33.55</v>
+        <v>-33.451</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-26.777</v>
+        <v>-26.744</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-64.68899999999999</v>
+        <v>-64.227</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-15.723</v>
+        <v>-15.039</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-68.54600000000001</v>
+        <v>-68.309</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-31.213</v>
+        <v>-31.037</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-24.076</v>
+        <v>-23.797</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-20.832</v>
+        <v>-20.562</v>
       </c>
       <c r="Q29" s="1" t="inlineStr">
         <is>
@@ -48896,7 +48896,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -55279,7 +55279,7 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
@@ -60142,7 +60142,7 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E519" s="5" t="n">

--- a/output/pdf_financials_xlsx/NDM.xlsx
+++ b/output/pdf_financials_xlsx/NDM.xlsx
@@ -1318,19 +1318,19 @@
         <v>-14.085</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-20.139</v>
+        <v>-20.19</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>-15.662</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-2.523</v>
+        <v>-2.339</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-31.347</v>
+        <v>-33.636</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>-33.829</v>
+        <v>-35.343</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>-26.982</v>
@@ -1351,7 +1351,7 @@
         <v>-24.335</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>-20.996</v>
+        <v>-21.106</v>
       </c>
       <c r="Q16" s="1" t="inlineStr">
         <is>
@@ -1380,19 +1380,19 @@
         <v>-0.03</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0</v>
+        <v>0.051</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.184</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-0</v>
+        <v>2.289</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0</v>
+        <v>1.514</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>-0</v>
@@ -1413,7 +1413,7 @@
         <v>-0.107</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>-0</v>
+        <v>0.11</v>
       </c>
       <c r="Q17" s="1" t="inlineStr">
         <is>
@@ -2062,19 +2062,19 @@
         <v>-13.541</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-19.195</v>
+        <v>-19.246</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-14.775</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.387</v>
+        <v>-1.203</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-31.066</v>
+        <v>-33.355</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-33.73</v>
+        <v>-35.244</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-26.949</v>
@@ -2095,7 +2095,7 @@
         <v>-24.056</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-20.726</v>
+        <v>-20.836</v>
       </c>
       <c r="Q27" s="1" t="inlineStr">
         <is>
@@ -2186,19 +2186,19 @@
         <v>-13.541</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-19.195</v>
+        <v>-19.246</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-14.775</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.387</v>
+        <v>-1.203</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-30.784</v>
+        <v>-33.073</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-33.451</v>
+        <v>-34.965</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-26.744</v>
@@ -2219,7 +2219,7 @@
         <v>-23.797</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-20.562</v>
+        <v>-20.672</v>
       </c>
       <c r="Q29" s="1" t="inlineStr">
         <is>
@@ -2340,19 +2340,19 @@
         <v>-0.2129925452609159</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-0</v>
+        <v>-0.2526002971768202</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-0</v>
+        <v>-7.866609662248825</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>-0</v>
+        <v>-6.805208704958972</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-0</v>
+        <v>-4.283733695498401</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>-0</v>
@@ -2373,7 +2373,7 @@
         <v>-0.4396959112389563</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-0</v>
+        <v>-0.5211788117123093</v>
       </c>
       <c r="Q31" s="1" t="inlineStr">
         <is>
@@ -30770,7 +30770,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E223" t="inlineStr">
         <is>
           <t>-</t>
@@ -35354,7 +35358,11 @@
           <t>Deferred income tax recovery 12</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>-</t>
@@ -41617,7 +41625,11 @@
           <t>Common shares issued for cash 7</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr"/>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E332" t="inlineStr">
         <is>
           <t>-</t>
@@ -49464,7 +49476,11 @@
           <t>Income tax (recovery) expense</t>
         </is>
       </c>
-      <c r="D411" t="inlineStr"/>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E411" t="inlineStr">
         <is>
           <t>-</t>
@@ -53079,7 +53095,11 @@
           <t>Deferred Income tax (recovery) expense</t>
         </is>
       </c>
-      <c r="D448" t="inlineStr"/>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E448" t="inlineStr">
         <is>
           <t>-</t>
@@ -54283,7 +54303,11 @@
           <t>Deferred income tax recovery 12</t>
         </is>
       </c>
-      <c r="D460" t="inlineStr"/>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E460" t="inlineStr">
         <is>
           <t>-</t>
@@ -55483,7 +55507,11 @@
           <t>Deferred Income tax (recovery) expense 13</t>
         </is>
       </c>
-      <c r="D472" t="inlineStr"/>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E472" t="inlineStr">
         <is>
           <t>-</t>
@@ -57556,7 +57584,11 @@
           <t>Income tax recovery 13</t>
         </is>
       </c>
-      <c r="D493" t="inlineStr"/>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E493" t="inlineStr">
         <is>
           <t>-</t>
@@ -58552,7 +58584,11 @@
           <t>Income tax (recovery) expense 12</t>
         </is>
       </c>
-      <c r="D503" t="inlineStr"/>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E503" t="inlineStr">
         <is>
           <t>-</t>
@@ -61346,7 +61382,11 @@
           <t>Income tax (recovery) 11</t>
         </is>
       </c>
-      <c r="D531" t="inlineStr"/>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E531" t="inlineStr">
         <is>
           <t>-</t>
